--- a/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1398,17 +1390,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1492,17 +1476,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1586,17 +1562,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1680,17 +1648,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1774,17 +1734,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1868,17 +1820,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1962,17 +1906,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2056,17 +1992,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2150,17 +2078,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2244,17 +2164,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2338,17 +2250,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2432,17 +2336,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2526,17 +2422,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2620,17 +2508,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2714,17 +2594,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2807,16 +2679,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2867,16 +2731,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2927,16 +2783,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2987,16 +2835,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3047,16 +2887,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3107,16 +2939,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3167,16 +2991,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3227,16 +3043,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3287,16 +3095,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3347,16 +3147,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,16 +3199,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3467,16 +3251,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3527,16 +3303,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3587,16 +3355,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3647,16 +3407,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3707,16 +3459,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3767,16 +3511,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3827,16 +3563,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3887,16 +3615,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3947,16 +3667,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4007,16 +3719,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4067,16 +3771,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4127,16 +3823,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,16 +3875,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4247,16 +3927,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4307,16 +3979,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4367,16 +4031,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4427,16 +4083,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4487,16 +4135,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4547,16 +4187,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4607,16 +4239,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4667,16 +4291,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4727,16 +4343,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4787,16 +4395,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4847,16 +4447,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4907,16 +4499,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4967,16 +4551,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5027,16 +4603,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5087,16 +4655,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5147,16 +4707,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5207,16 +4759,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5262,16 +4806,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5317,16 +4853,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5372,16 +4900,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5427,16 +4947,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5482,16 +4994,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5537,16 +5041,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5592,16 +5088,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5647,16 +5135,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5702,16 +5182,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5757,16 +5229,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5812,16 +5276,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5867,16 +5323,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5922,16 +5370,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3095,8 +3599,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3147,8 +3674,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3199,8 +3749,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3251,8 +3824,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3303,8 +3899,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3355,8 +3974,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,8 +4049,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3459,8 +4124,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3511,8 +4199,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3563,8 +4274,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3615,8 +4349,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3667,8 +4424,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3719,8 +4499,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3771,8 +4574,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3823,8 +4649,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3875,8 +4724,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3927,8 +4799,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3979,8 +4874,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4031,8 +4949,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4083,8 +5024,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4135,8 +5099,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,8 +5174,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4239,8 +5249,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4291,8 +5324,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4343,8 +5399,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4395,8 +5474,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4447,8 +5549,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4499,8 +5624,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4551,8 +5699,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4603,8 +5774,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4655,8 +5849,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4707,8 +5924,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4759,8 +5999,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4806,8 +6069,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4853,8 +6139,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4900,8 +6209,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4947,8 +6279,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4994,8 +6349,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5041,8 +6419,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5088,8 +6489,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5135,8 +6559,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5182,8 +6629,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5229,8 +6699,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5276,8 +6769,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5323,8 +6839,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5370,8 +6909,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">

--- a/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00026_2126_상생친구_보장보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
